--- a/sample_apps/dst_stn_ja/dst_knowledge_ja.xlsx
+++ b/sample_apps/dst_stn_ja/dst_knowledge_ja.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakano\system\dialbb\dialbb-next\sample_apps\dst_stn_ja\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76643BEB-2558-4EE6-8E51-5749C6136A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D380451-56E2-4C2B-B4B0-126F6D1D3213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3566FB2-A815-41D8-9347-99D11DD601B4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3566FB2-A815-41D8-9347-99D11DD601B4}"/>
   </bookViews>
   <sheets>
     <sheet name="dialogues" sheetId="2" r:id="rId1"/>
@@ -277,12 +277,6 @@
 ユーザ：大好き</t>
   </si>
   <si>
-    <t>システム：好きなラーメンは何ですか？
-ユーザ：札幌の味噌ラーメン
-システム：好きなラーメンは何ですか？
-ユーザ：札幌の味噌ラーメン</t>
-  </si>
-  <si>
     <t>システム：好きなラーメン教えて
 ユーザ：豚骨ラーメン
 システム：博多の？
@@ -315,6 +309,12 @@
   </si>
   <si>
     <t>ユーザの名前=優香</t>
+  </si>
+  <si>
+    <t>システム：好きなラーメンは何ですか？
+ユーザ：味噌ラーメン
+システム：札幌の味噌ラーメンですか？
+ユーザ：そう</t>
   </si>
 </sst>
 </file>
@@ -711,10 +711,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F8F96FF-CF47-4A99-83E7-8D5E860D6DFF}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="62.59765625" customWidth="1"/>
-    <col min="3" max="3" width="34.86328125" customWidth="1"/>
+    <col min="2" max="2" width="62.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -728,7 +728,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.5">
+    <row r="2" spans="1:3" ht="30">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -739,7 +739,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28.5">
+    <row r="3" spans="1:3" ht="30">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -750,7 +750,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28.5">
+    <row r="4" spans="1:3" ht="30">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -761,7 +761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="28.5">
+    <row r="5" spans="1:3" ht="30">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -772,7 +772,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="28.5">
+    <row r="6" spans="1:3" ht="30">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -783,12 +783,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="57">
+    <row r="7" spans="1:3" ht="60">
       <c r="A7" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -799,32 +799,32 @@
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="28.5">
+    <row r="9" spans="1:3" ht="30">
       <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="60">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="57">
-      <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" t="s">
         <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -837,10 +837,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E27BD90-5E4C-4A7C-B9E8-ABC211947ECB}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -965,10 +965,10 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
         <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -976,10 +976,10 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/sample_apps/dst_stn_ja/dst_knowledge_ja.xlsx
+++ b/sample_apps/dst_stn_ja/dst_knowledge_ja.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakano\system\dialbb\dialbb-next\sample_apps\dst_stn_ja\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D380451-56E2-4C2B-B4B0-126F6D1D3213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86709119-3ECA-43C5-B8C0-1ACE2C1CE480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3566FB2-A815-41D8-9347-99D11DD601B4}"/>
+    <workbookView xWindow="28605" yWindow="-195" windowWidth="29190" windowHeight="15870" activeTab="1" xr2:uid="{C3566FB2-A815-41D8-9347-99D11DD601B4}"/>
   </bookViews>
   <sheets>
     <sheet name="dialogues" sheetId="2" r:id="rId1"/>
@@ -143,16 +143,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>好きなラーメン=豚骨ラーメン</t>
-    <rPh sb="0" eb="1">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>トンコツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>slots</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -198,55 +188,23 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>地方=博多、好きなラーメン=豚骨ラーメン</t>
-    <rPh sb="0" eb="2">
-      <t>チホウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
+    <t>富山</t>
+    <rPh sb="0" eb="2">
+      <t>トヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佐野</t>
+    <rPh sb="0" eb="2">
+      <t>サノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>博多</t>
+    <rPh sb="0" eb="2">
       <t>ハカタ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>トンコツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>富山</t>
-    <rPh sb="0" eb="2">
-      <t>トヤマ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>佐野</t>
-    <rPh sb="0" eb="2">
-      <t>サノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>博多</t>
-    <rPh sb="0" eb="2">
-      <t>ハカタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>地方=札幌, 好きなラーメン=味噌ラーメン</t>
-    <rPh sb="0" eb="2">
-      <t>チホウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サッポロ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ミソ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -312,9 +270,18 @@
   </si>
   <si>
     <t>システム：好きなラーメンは何ですか？
-ユーザ：味噌ラーメン
-システム：札幌の味噌ラーメンですか？
-ユーザ：そう</t>
+ユーザ：札幌ラーメンですね
+システム：味噌ラーメンですか？
+ユーザ：はい</t>
+  </si>
+  <si>
+    <t>地方=札幌, 好きなラーメン=味噌ラーメン</t>
+  </si>
+  <si>
+    <t>好きなラーメン=豚骨ラーメン</t>
+  </si>
+  <si>
+    <t>地方=博多、好きなラーメン=豚骨ラーメン</t>
   </si>
 </sst>
 </file>
@@ -722,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30">
@@ -733,10 +700,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30">
@@ -744,10 +711,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30">
@@ -755,10 +722,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30">
@@ -766,10 +733,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30">
@@ -777,10 +744,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="60">
@@ -788,10 +755,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="66.75" customHeight="1">
@@ -799,32 +766,32 @@
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="60">
       <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +829,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -876,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -890,7 +857,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -904,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -918,7 +885,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -932,10 +899,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -943,10 +910,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -954,10 +921,10 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -965,10 +932,10 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -976,10 +943,10 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/sample_apps/dst_stn_ja/dst_knowledge_ja.xlsx
+++ b/sample_apps/dst_stn_ja/dst_knowledge_ja.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakano\system\dialbb\dialbb-next\sample_apps\dst_stn_ja\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86709119-3ECA-43C5-B8C0-1ACE2C1CE480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA23D51E-77AF-496E-BF99-A031E9DDC325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28605" yWindow="-195" windowWidth="29190" windowHeight="15870" activeTab="1" xr2:uid="{C3566FB2-A815-41D8-9347-99D11DD601B4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3566FB2-A815-41D8-9347-99D11DD601B4}"/>
   </bookViews>
   <sheets>
     <sheet name="dialogues" sheetId="2" r:id="rId1"/>
